--- a/output/2026-10-11_12_Serbia_Pomoravski_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-11_12_Serbia_Pomoravski_Utensilerie_e_Macchine_Utensili.xlsx
@@ -474,7 +474,6 @@
           <t>Woby Haus - prodaja mašina i alata</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Jagodina, Pomoravski</t>
@@ -490,10 +489,9 @@
           <t>035/247-666</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Indirizzo: Kablovska bb, 35000 Jagodina. Esistenza confermata tramite directory PlanPlus.rs (profilo aziendale con indirizzo, telefono e orari di apertura). Nessun sito web o email ufficiale reperiti. La catena è presente anche in altre città serbe (Subotica, Čačak) ma senza riscontro di collegamento societario diretto nei risultati di ricerca.</t>
+          <t>Indirizzo: Kablovska bb, 35000 Jagodina. Esistenza confermata tramite directory PlanPlus.rs (profilo aziendale con indirizzo, telefono e orari di apertura). Nessun sito web o email ufficiale reperiti. La catena è presente anche in altre città serbe (Subotica, Čačak) ma senza riscontro di collegamento societario diretto nei risultati di ricerca. [DUPLICATO — vedi anche: 2026-10-08_01_Serbia_Kolubarski_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -508,7 +506,6 @@
           <t>Roanda Komerc - STIHL prodaja i servis (sede Jagodina + filiali Svilajnac e Despotovac)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Pomoravski (Jagodina, Svilajnac, Despotovac)</t>
@@ -524,7 +521,6 @@
           <t>035/8200-139 (Jagodina) | 035/323-008 (Svilajnac) | 035/613-713 (Despotovac)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Tre filiali della lista grezza deduplicate in un'unica riga aziendale. Sede Jagodina: Maksima Gorkog 1 (confermata su PlanPlus.rs, indirizzo e telefono corrispondenti). Filiale Despotovac: Despota Stefana Lazarevića 37 (confermata su PlanPlus.rs, indirizzo e telefono corrispondenti). Filiale Svilajnac: Dimitrija Katića bb (presente nella lista grezza originale; non trovato riscontro indipendente nei risultati di ricerca, ma stessa azienda verificata nelle altre due sedi). Nessun sito web o email ufficiale reperiti.</t>
